--- a/data/Ficha_05_DL1153_202605_Vacuna_ninos_24meses.xlsx
+++ b/data/Ficha_05_DL1153_202605_Vacuna_ninos_24meses.xlsx
@@ -406,7 +406,7 @@
     <t>PERIODO: ENERO - MAYO 2026</t>
   </si>
   <si>
-    <t>FUENTE: PADRON NOMINAL: 18/05/2026  |  HISMINSA: 17/05/2026</t>
+    <t>FUENTE: PADRON NOMINAL: 25/05/2026  |  HISMINSA: 24/05/2026</t>
   </si>
 </sst>
 </file>
@@ -762,7 +762,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46160.518563888887" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="357">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46167.519539583336" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="357">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -1321,7 +1321,7 @@
     <x v="4"/>
     <n v="90118"/>
     <n v="13"/>
-    <n v="3"/>
+    <n v="4"/>
   </r>
   <r>
     <x v="0"/>
@@ -3465,7 +3465,7 @@
     <x v="19"/>
     <x v="2"/>
     <n v="90401"/>
-    <n v="1"/>
+    <n v="2"/>
     <n v="1"/>
   </r>
   <r>
@@ -3509,7 +3509,7 @@
     <x v="24"/>
     <x v="2"/>
     <n v="90413"/>
-    <n v="2"/>
+    <n v="1"/>
     <n v="0"/>
   </r>
   <r>
@@ -4858,6 +4858,133 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="J8:N14" firstHeaderRow="0" firstDataRow="1" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="3" hier="-1"/>
+    <pageField fld="5" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Suma de Denominador" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Numerador" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Indicador" fld="9" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A8:F16" firstHeaderRow="0" firstDataRow="1" firstDataCol="3" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="10">
@@ -5055,133 +5182,6 @@
   <pageFields count="2">
     <pageField fld="0" hier="-1"/>
     <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Suma de Denominador" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Numerador" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Indicador" fld="9" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="16">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="15">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="J8:N14" firstHeaderRow="0" firstDataRow="1" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="1">
-        <item x="0"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="0"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="5" hier="-1"/>
   </pageFields>
   <dataFields count="3">
     <dataField name="Suma de Denominador" fld="7" baseField="0" baseItem="0"/>
@@ -5751,10 +5751,10 @@
         <v>618</v>
       </c>
       <c r="E13" s="4">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F13" s="5">
-        <v>0.5436893203883495</v>
+        <v>0.54530744336569581</v>
       </c>
       <c r="K13" t="s">
         <v>123</v>
@@ -5763,10 +5763,10 @@
         <v>359</v>
       </c>
       <c r="M13" s="4">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N13" s="5">
-        <v>0.50139275766016711</v>
+        <v>0.50417827298050144</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -5789,10 +5789,10 @@
         <v>1915</v>
       </c>
       <c r="M14" s="4">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N14" s="5">
-        <v>0.56240208877284592</v>
+        <v>0.5629242819843342</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -5817,10 +5817,10 @@
         <v>1915</v>
       </c>
       <c r="E16" s="4">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F16" s="5">
-        <v>0.56240208877284592</v>
+        <v>0.5629242819843342</v>
       </c>
     </row>
   </sheetData>
@@ -6914,7 +6914,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -12566,7 +12566,7 @@
         <v>90401</v>
       </c>
       <c r="H232" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I232" s="1">
         <v>1</v>
@@ -12682,7 +12682,7 @@
         <v>90413</v>
       </c>
       <c r="H236" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I236" s="1">
         <v>0</v>
